--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_mediabrut_a_2020_coquimbo.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_mediabrut_a_2020_coquimbo.xlsx
@@ -105,7 +105,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 14:12</t>
+    <t xml:space="preserve">2026-09-24 01:02</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -675,19 +675,19 @@
         <v>16</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>-0.16</v>
+        <v>-0.13</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>-0.08</v>
+        <v>-0.07</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>-0.09</v>
+        <v>-0.06</v>
       </c>
     </row>
     <row r="9">
@@ -698,19 +698,19 @@
         <v>16</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>-0.15</v>
+        <v>-0.06</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E9" s="2" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>340</v>
+      </c>
+      <c r="G9" s="2" t="n">
         <v>-0.03</v>
-      </c>
-      <c r="F9" s="2" t="n">
-        <v>338</v>
-      </c>
-      <c r="G9" s="2" t="n">
-        <v>-0.12</v>
       </c>
     </row>
     <row r="10">
@@ -721,19 +721,19 @@
         <v>16</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>-0.09</v>
+        <v>-0.12</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E10" s="2" t="n">
         <v>-0.06</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>-0.03</v>
+        <v>-0.06</v>
       </c>
     </row>
     <row r="11">
@@ -744,19 +744,19 @@
         <v>16</v>
       </c>
       <c r="C11" s="2" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>-0.07</v>
+      </c>
+      <c r="F11" s="2" t="n">
+        <v>340</v>
+      </c>
+      <c r="G11" s="2" t="n">
         <v>-0.03</v>
-      </c>
-      <c r="D11" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="E11" s="2" t="n">
-        <v>-0.06</v>
-      </c>
-      <c r="F11" s="2" t="n">
-        <v>338</v>
-      </c>
-      <c r="G11" s="2" t="n">
-        <v>0.04</v>
       </c>
     </row>
     <row r="12">
